--- a/data/country-names.xlsx
+++ b/data/country-names.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B262"/>
+  <dimension ref="A1:B308"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2495,9 +2495,377 @@
         <v>Saipan</v>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>南韓</v>
+      </c>
+      <c r="B263" t="str">
+        <v>South Korea</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>中國</v>
+      </c>
+      <c r="B264" t="str">
+        <v>China</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>澳门</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Macao</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>马来西亚</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Malaysia</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>菲律宾</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Philippines</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>寮国</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Laos</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>缅甸</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Myanmar</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>斯里兰卡</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Sri Lanka</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>尼泊尔</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Nepal</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>哈萨克</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Kazakhstan</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>阿聯</v>
+      </c>
+      <c r="B273" t="str">
+        <v>United Arab Emirates</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>阿联酋</v>
+      </c>
+      <c r="B274" t="str">
+        <v>United Arab Emirates</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>卡塔尔</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Qatar</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>英国</v>
+      </c>
+      <c r="B276" t="str">
+        <v>United Kingdom</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>德国</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>意大利</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Italy</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>荷兰</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Netherlands</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>俄罗斯</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Russia</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>美国</v>
+      </c>
+      <c r="B281" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>南美洲</v>
+      </c>
+      <c r="B282" t="str">
+        <v>South America</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>南美州</v>
+      </c>
+      <c r="B283" t="str">
+        <v>South America</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>非州</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Africa</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>澳大利亞</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>新西兰</v>
+      </c>
+      <c r="B286" t="str">
+        <v>New Zealand</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>澳紐</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Australia &amp; New Zealand</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>東南亞</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Southeast Asia</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>东南亚</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Southeast Asia</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>兩岸三地</v>
+      </c>
+      <c r="B290" t="str">
+        <v>China, Hong Kong, Macao &amp; Taiwan</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>中港台</v>
+      </c>
+      <c r="B291" t="str">
+        <v>China, Hong Kong &amp; Taiwan</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>欧洲</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Europe</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>中東</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Middle East</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>中东</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Middle East</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>全球</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Global</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>世界</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Worldwide</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>马新</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Malaysia &amp; Singapore</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>馬新</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Malaysia &amp; Singapore</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>韓日</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Korea &amp; Japan</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>韩日</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Korea &amp; Japan</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>中港</v>
+      </c>
+      <c r="B301" t="str">
+        <v>China &amp; Hong Kong</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>中台</v>
+      </c>
+      <c r="B302" t="str">
+        <v>China &amp; Taiwan</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>美加</v>
+      </c>
+      <c r="B303" t="str">
+        <v>United States &amp; Canada</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>加美</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Canada &amp; United States</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>台日</v>
+      </c>
+      <c r="B305" t="str">
+        <v>Taiwan &amp; Japan</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>日台</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Japan &amp; Taiwan</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>台韓</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Taiwan &amp; Korea</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>韓台</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Korea &amp; Taiwan</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B262"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B308"/>
   </ignoredErrors>
 </worksheet>
 </file>